--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MISSOURI_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MISSOURI_2019.xlsx
@@ -1579,7 +1579,7 @@
         <v>38</v>
       </c>
       <c r="D68">
-        <v>0.009919081179848603</v>
+        <v>0.009919081179848604</v>
       </c>
     </row>
     <row r="69">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C128">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C213">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C510">
